--- a/Exercício_Finanças_Aluno.xlsx
+++ b/Exercício_Finanças_Aluno.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduardo_alves156\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduardo_alves156.EDU_FIESC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC83E95-15C4-4D3F-99FF-AAF0E3293725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DF6D9C-730A-4D9A-8D84-DE9FD1159F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Utilize fórmulas para realizar os cálculos</t>
   </si>
@@ -127,15 +127,40 @@
   </si>
   <si>
     <t>Reajustes %</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>Telefone/int</t>
+  </si>
+  <si>
+    <t>Outras despe.</t>
+  </si>
+  <si>
+    <t>Sálario</t>
+  </si>
+  <si>
+    <t>Novo Reajuste %</t>
+  </si>
+  <si>
+    <t>Junho</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -167,7 +192,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,6 +214,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -223,7 +260,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -247,34 +284,101 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
@@ -568,260 +672,498 @@
     <col min="8" max="16384" width="10.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="E15" s="21" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="E15" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="I15" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="20" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="I16" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
         <v>1700</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="15">
         <v>196</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="E17" s="23">
+      <c r="C17" s="15"/>
+      <c r="E17" s="21">
         <v>1700</v>
       </c>
-      <c r="F17" s="23">
-        <v>196</v>
-      </c>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16">
+      <c r="F17" s="28">
+        <f>F33</f>
+        <v>211.68</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="I17" s="35">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="J17" s="35">
+        <f>F33</f>
+        <v>211.68</v>
+      </c>
+      <c r="K17" s="34"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15">
         <v>150</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23">
-        <v>150</v>
-      </c>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16">
+      <c r="C18" s="15"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="28">
+        <f>F34</f>
+        <v>160.5</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35">
+        <f>F34</f>
+        <v>160.5</v>
+      </c>
+      <c r="K18" s="34"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15">
         <v>900</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23">
-        <v>900</v>
-      </c>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
-      <c r="B20" s="17">
+      <c r="C19" s="15"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="28">
+        <f>F35</f>
+        <v>949.5</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35">
+        <f>F35</f>
+        <v>949.5</v>
+      </c>
+      <c r="K19" s="34"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="16">
         <v>200</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="24">
+      <c r="C20" s="14"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="22">
         <v>200</v>
       </c>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="G20" s="20"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="36">
+        <v>200</v>
+      </c>
+      <c r="K20" s="33"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
         <v>1700</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <f>SUM(B17:B20)</f>
         <v>1446</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <f>A21-B21</f>
         <v>254</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="20">
         <v>1700</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="20">
         <f>SUM(F17:F20)</f>
-        <v>1446</v>
-      </c>
-      <c r="G21" s="22">
+        <v>1521.68</v>
+      </c>
+      <c r="G21" s="20">
         <f>E21-F21</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+        <v>178.31999999999994</v>
+      </c>
+      <c r="I21" s="38">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="J21" s="38">
+        <f>SUM(J17:J20)</f>
+        <v>1521.68</v>
+      </c>
+      <c r="K21" s="38">
+        <f>I21-J21</f>
+        <v>348.32000000000016</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="E24" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="I24" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
+      <c r="E25" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
         <v>1700</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B26" s="18">
         <v>196</v>
       </c>
-      <c r="C25" s="19"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19">
+      <c r="C26" s="18"/>
+      <c r="E26" s="43">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="F26" s="42">
+        <f>F33</f>
+        <v>211.68</v>
+      </c>
+      <c r="G26" s="31"/>
+      <c r="I26" s="46">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="J26" s="46">
+        <f>F33</f>
+        <v>211.68</v>
+      </c>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18">
         <v>150</v>
       </c>
-      <c r="C26" s="19"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19">
+      <c r="C27" s="18"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="42">
+        <f>F34</f>
+        <v>160.5</v>
+      </c>
+      <c r="G27" s="31"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="46">
+        <f>F34</f>
+        <v>160.5</v>
+      </c>
+      <c r="K27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18">
         <v>900</v>
       </c>
-      <c r="C27" s="19"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="18">
+      <c r="C28" s="18"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="42">
+        <f>F35</f>
+        <v>949.5</v>
+      </c>
+      <c r="G28" s="31"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="46">
+        <f>F35</f>
+        <v>949.5</v>
+      </c>
+      <c r="K28" s="18"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>1700</v>
       </c>
-      <c r="B28" s="18">
-        <f>SUM(B25:B27)</f>
+      <c r="B29" s="17">
+        <f>SUM(B26:B28)</f>
         <v>1246</v>
       </c>
-      <c r="C28" s="18">
-        <f>A28-B28</f>
+      <c r="C29" s="17">
+        <f>A29-B29</f>
         <v>454</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="E29" s="44"/>
+      <c r="F29" s="45">
+        <v>595</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="I29" s="47">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="J29" s="19">
+        <f>SUM(J26:J28)</f>
+        <v>1321.68</v>
+      </c>
+      <c r="K29" s="19">
+        <f>I29-J29</f>
+        <v>548.32000000000016</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="E30" s="44">
+        <f>F36</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="F30" s="44">
+        <f>SUM(F26:F29)</f>
+        <v>1916.68</v>
+      </c>
+      <c r="G30" s="44">
+        <f>E30-F30</f>
+        <v>-46.679999999999836</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="B32" s="39"/>
+      <c r="C32" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="12">
         <v>196</v>
       </c>
-      <c r="B31" s="13">
-        <f>1+A31/100</f>
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="C33" s="12"/>
+      <c r="D33" s="40">
+        <v>8</v>
+      </c>
+      <c r="E33" s="13">
+        <f>1+D33/100</f>
+        <v>1.08</v>
+      </c>
+      <c r="F33" s="26">
+        <f>B33*E33</f>
+        <v>211.68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="12">
         <v>150</v>
       </c>
-      <c r="B32" s="12"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
+      <c r="C34" s="12"/>
+      <c r="D34" s="40">
+        <v>7</v>
+      </c>
+      <c r="E34" s="13">
+        <f>1+D34/100</f>
+        <v>1.07</v>
+      </c>
+      <c r="F34" s="26">
+        <f>B34*E34</f>
+        <v>160.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="12">
         <v>900</v>
       </c>
-      <c r="B33" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="41">
+        <v>5.5</v>
+      </c>
+      <c r="E35" s="13">
+        <f>1+D35/100</f>
+        <v>1.0549999999999999</v>
+      </c>
+      <c r="F35" s="26">
+        <f>B35*E35</f>
+        <v>949.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="12">
+        <v>1700</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="40">
+        <v>10</v>
+      </c>
+      <c r="E36" s="13">
+        <f>1+D36/100</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F36" s="26">
+        <f>B36*E36</f>
+        <v>1870.0000000000002</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I24:K24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
